--- a/artfynd/A 4133-2021 artfynd.xlsx
+++ b/artfynd/A 4133-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128413842</v>
       </c>
       <c r="B2" t="n">
-        <v>99504</v>
+        <v>99506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4133-2021 artfynd.xlsx
+++ b/artfynd/A 4133-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128413842</v>
       </c>
       <c r="B2" t="n">
-        <v>99506</v>
+        <v>99599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4133-2021 artfynd.xlsx
+++ b/artfynd/A 4133-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128413842</v>
       </c>
       <c r="B2" t="n">
-        <v>99599</v>
+        <v>99613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4133-2021 artfynd.xlsx
+++ b/artfynd/A 4133-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128413842</v>
       </c>
       <c r="B2" t="n">
-        <v>99613</v>
+        <v>99616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4133-2021 artfynd.xlsx
+++ b/artfynd/A 4133-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128413842</v>
       </c>
       <c r="B2" t="n">
-        <v>99616</v>
+        <v>99621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4133-2021 artfynd.xlsx
+++ b/artfynd/A 4133-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128413842</v>
       </c>
       <c r="B2" t="n">
-        <v>99621</v>
+        <v>99622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4133-2021 artfynd.xlsx
+++ b/artfynd/A 4133-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128413842</v>
       </c>
       <c r="B2" t="n">
-        <v>99622</v>
+        <v>99649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4133-2021 artfynd.xlsx
+++ b/artfynd/A 4133-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128413842</v>
       </c>
       <c r="B2" t="n">
-        <v>99649</v>
+        <v>99662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4133-2021 artfynd.xlsx
+++ b/artfynd/A 4133-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128413842</v>
       </c>
       <c r="B2" t="n">
-        <v>99662</v>
+        <v>99666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4133-2021 artfynd.xlsx
+++ b/artfynd/A 4133-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128413842</v>
       </c>
       <c r="B2" t="n">
-        <v>99666</v>
+        <v>99673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
